--- a/Simul_team/scenarios/엑셀 결합 데이터.xlsx
+++ b/Simul_team/scenarios/엑셀 결합 데이터.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MCI_ADV\Simul_team\scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weff2\MCI_ADV\Simul_team\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F059A560-E8D0-43DF-9A0E-9C7BBA29DD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50026155-83A7-4DB5-99D5-2BE05B39230A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19950" yWindow="4545" windowWidth="10215" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3998,9 +3998,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R569"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>71</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>72</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>73</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>75</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>76</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>78</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>79</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>80</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>111</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>112</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>113</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>115</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>116</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>117</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>118</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>119</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>120</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>121</v>
       </c>
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>122</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>123</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>124</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>125</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>126</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>127</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>128</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>129</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>131</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>132</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>133</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>134</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>135</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>136</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>137</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>140</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>142</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>143</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>144</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>145</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>146</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>147</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>148</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>149</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>150</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>151</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>152</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>153</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>154</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>155</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>156</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>157</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>158</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>159</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>160</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>161</v>
       </c>
@@ -10174,7 +10174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>162</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>163</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>164</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>165</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>167</v>
       </c>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>168</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>169</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>170</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>171</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>172</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>173</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>174</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>175</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>176</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>177</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>178</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>179</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>180</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>181</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>182</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>183</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>184</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>185</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>186</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>187</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>188</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>189</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>190</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>191</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>192</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>193</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>194</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>195</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>196</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>198</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>200</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>201</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>202</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>203</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>204</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>205</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>206</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>207</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>208</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>209</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>210</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>211</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>212</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>213</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>214</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>215</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>216</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>217</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>218</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>219</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>220</v>
       </c>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>221</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>222</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>223</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>224</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>225</v>
       </c>
@@ -12807,7 +12807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>226</v>
       </c>
@@ -12848,7 +12848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>227</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>228</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>229</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>230</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>231</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>232</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>233</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>234</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>235</v>
       </c>
@@ -13217,7 +13217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>236</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>237</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>238</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>239</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>240</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>241</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>242</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>243</v>
       </c>
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>244</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>245</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>246</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>247</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>248</v>
       </c>
@@ -13750,7 +13750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>249</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>250</v>
       </c>
@@ -13832,7 +13832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>251</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>252</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>253</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>254</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>255</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>256</v>
       </c>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>257</v>
       </c>
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>258</v>
       </c>
@@ -14160,7 +14160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>259</v>
       </c>
@@ -14201,7 +14201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>260</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>261</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>262</v>
       </c>
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>263</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>264</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>265</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>266</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>267</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>268</v>
       </c>
@@ -14573,7 +14573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>269</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>270</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>271</v>
       </c>
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>272</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>273</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>274</v>
       </c>
@@ -14819,7 +14819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>275</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>276</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>277</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>278</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>279</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>280</v>
       </c>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>281</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>282</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>283</v>
       </c>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>284</v>
       </c>
@@ -15229,7 +15229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>285</v>
       </c>
@@ -15270,7 +15270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>286</v>
       </c>
@@ -15311,7 +15311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>287</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>288</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>289</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>290</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>291</v>
       </c>
@@ -15516,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>292</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>293</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>294</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>295</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>296</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>297</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>298</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>299</v>
       </c>
@@ -15844,7 +15844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>300</v>
       </c>
@@ -15885,7 +15885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>301</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>302</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>303</v>
       </c>
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>304</v>
       </c>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>305</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>306</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>307</v>
       </c>
@@ -16172,7 +16172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>308</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>309</v>
       </c>
@@ -16254,7 +16254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>310</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>311</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>312</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>313</v>
       </c>
@@ -16418,7 +16418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>314</v>
       </c>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>315</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>316</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>317</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>318</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>319</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>320</v>
       </c>
@@ -16705,7 +16705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>321</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>322</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>323</v>
       </c>
@@ -16828,7 +16828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>324</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>325</v>
       </c>
@@ -16910,7 +16910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>326</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>327</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>328</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>329</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>330</v>
       </c>
@@ -17115,7 +17115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>331</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>332</v>
       </c>
@@ -17197,7 +17197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>333</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>334</v>
       </c>
@@ -17279,7 +17279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>335</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>336</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>337</v>
       </c>
@@ -17402,7 +17402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>338</v>
       </c>
@@ -17443,7 +17443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>339</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>340</v>
       </c>
@@ -17525,7 +17525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>341</v>
       </c>
@@ -17566,7 +17566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>342</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>343</v>
       </c>
@@ -17648,7 +17648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>344</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>345</v>
       </c>
@@ -17730,7 +17730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>346</v>
       </c>
@@ -17771,7 +17771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>347</v>
       </c>
@@ -17812,7 +17812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>348</v>
       </c>
@@ -17853,7 +17853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>349</v>
       </c>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>350</v>
       </c>
@@ -17935,7 +17935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>351</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>352</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>353</v>
       </c>
@@ -18058,7 +18058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>354</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>355</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>356</v>
       </c>
@@ -18181,7 +18181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>357</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>358</v>
       </c>
@@ -18263,7 +18263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>359</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>360</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>361</v>
       </c>
@@ -18386,7 +18386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>362</v>
       </c>
@@ -18427,7 +18427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>363</v>
       </c>
@@ -18468,7 +18468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>364</v>
       </c>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>365</v>
       </c>
@@ -18550,7 +18550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>366</v>
       </c>
@@ -18591,7 +18591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>367</v>
       </c>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>368</v>
       </c>
@@ -18673,7 +18673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>369</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>370</v>
       </c>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>371</v>
       </c>
@@ -18796,7 +18796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>372</v>
       </c>
@@ -18837,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>373</v>
       </c>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>374</v>
       </c>
@@ -18919,7 +18919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>375</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>376</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>377</v>
       </c>
@@ -19045,7 +19045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>378</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>379</v>
       </c>
@@ -19130,7 +19130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>380</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>381</v>
       </c>
@@ -19212,7 +19212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>382</v>
       </c>
@@ -19253,7 +19253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>383</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>384</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>385</v>
       </c>
@@ -19379,7 +19379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>386</v>
       </c>
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>387</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>388</v>
       </c>
@@ -19502,7 +19502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>389</v>
       </c>
@@ -19543,7 +19543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>390</v>
       </c>
@@ -19584,7 +19584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>391</v>
       </c>
@@ -19625,7 +19625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>392</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>393</v>
       </c>
@@ -19707,7 +19707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>394</v>
       </c>
@@ -19748,7 +19748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>395</v>
       </c>
@@ -19789,7 +19789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>396</v>
       </c>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>397</v>
       </c>
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>398</v>
       </c>
@@ -19912,7 +19912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>399</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>400</v>
       </c>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>401</v>
       </c>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>402</v>
       </c>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>403</v>
       </c>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>404</v>
       </c>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>405</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>406</v>
       </c>
@@ -20243,7 +20243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>407</v>
       </c>
@@ -20284,7 +20284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>408</v>
       </c>
@@ -20325,7 +20325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>409</v>
       </c>
@@ -20366,7 +20366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>410</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>411</v>
       </c>
@@ -20448,7 +20448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>412</v>
       </c>
@@ -20489,7 +20489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>413</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>414</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>415</v>
       </c>
@@ -20612,7 +20612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>416</v>
       </c>
@@ -20653,7 +20653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>417</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>418</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>419</v>
       </c>
@@ -20779,7 +20779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>420</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>421</v>
       </c>
@@ -20861,7 +20861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>422</v>
       </c>
@@ -20902,7 +20902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>423</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>424</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>425</v>
       </c>
@@ -21025,7 +21025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>426</v>
       </c>
@@ -21069,7 +21069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>427</v>
       </c>
@@ -21110,7 +21110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>428</v>
       </c>
@@ -21151,7 +21151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>429</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>430</v>
       </c>
@@ -21233,7 +21233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>431</v>
       </c>
@@ -21274,7 +21274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>432</v>
       </c>
@@ -21315,7 +21315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>433</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>434</v>
       </c>
@@ -21397,7 +21397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>435</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>436</v>
       </c>
@@ -21479,7 +21479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>437</v>
       </c>
@@ -21520,7 +21520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>438</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>439</v>
       </c>
@@ -21602,7 +21602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>440</v>
       </c>
@@ -21643,7 +21643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>441</v>
       </c>
@@ -21687,7 +21687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>442</v>
       </c>
@@ -21728,7 +21728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>443</v>
       </c>
@@ -21769,7 +21769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>444</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>445</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>446</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>447</v>
       </c>
@@ -21933,7 +21933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>448</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>449</v>
       </c>
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>450</v>
       </c>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>451</v>
       </c>
@@ -22097,7 +22097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>452</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>453</v>
       </c>
@@ -22179,7 +22179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>454</v>
       </c>
@@ -22220,7 +22220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>455</v>
       </c>
@@ -22261,7 +22261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>456</v>
       </c>
@@ -22302,7 +22302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>457</v>
       </c>
@@ -22343,7 +22343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>458</v>
       </c>
@@ -22387,7 +22387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>459</v>
       </c>
@@ -22428,7 +22428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>460</v>
       </c>
@@ -22469,7 +22469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>461</v>
       </c>
@@ -22510,7 +22510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>462</v>
       </c>
@@ -22551,7 +22551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>463</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>464</v>
       </c>
@@ -22636,7 +22636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>465</v>
       </c>
@@ -22677,7 +22677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>466</v>
       </c>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>467</v>
       </c>
@@ -22759,7 +22759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>468</v>
       </c>
@@ -22800,7 +22800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>469</v>
       </c>
@@ -22844,7 +22844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>470</v>
       </c>
@@ -22885,7 +22885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>471</v>
       </c>
@@ -22926,7 +22926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>472</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>473</v>
       </c>
@@ -23011,7 +23011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>474</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>475</v>
       </c>
@@ -23096,7 +23096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>476</v>
       </c>
@@ -23140,7 +23140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>477</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>478</v>
       </c>
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>479</v>
       </c>
@@ -23266,7 +23266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>480</v>
       </c>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>481</v>
       </c>
@@ -23348,7 +23348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>482</v>
       </c>
@@ -23389,7 +23389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>483</v>
       </c>
@@ -23430,7 +23430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>484</v>
       </c>
@@ -23471,7 +23471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>485</v>
       </c>
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>486</v>
       </c>
@@ -23556,7 +23556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>487</v>
       </c>
@@ -23597,7 +23597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>488</v>
       </c>
@@ -23638,7 +23638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>489</v>
       </c>
@@ -23679,7 +23679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>490</v>
       </c>
@@ -23720,7 +23720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>491</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>492</v>
       </c>
@@ -23802,7 +23802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>493</v>
       </c>
@@ -23843,7 +23843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>494</v>
       </c>
@@ -23884,7 +23884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>495</v>
       </c>
@@ -23925,7 +23925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>496</v>
       </c>
@@ -23969,7 +23969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>497</v>
       </c>
@@ -24010,7 +24010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>498</v>
       </c>
@@ -24051,7 +24051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>499</v>
       </c>
@@ -24092,7 +24092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>500</v>
       </c>
@@ -24133,7 +24133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>501</v>
       </c>
@@ -24174,7 +24174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>502</v>
       </c>
@@ -24215,7 +24215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>503</v>
       </c>
@@ -24256,7 +24256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>504</v>
       </c>
@@ -24300,7 +24300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>505</v>
       </c>
@@ -24341,7 +24341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>506</v>
       </c>
@@ -24382,7 +24382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>507</v>
       </c>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>508</v>
       </c>
@@ -24464,7 +24464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>509</v>
       </c>
@@ -24505,7 +24505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>510</v>
       </c>
@@ -24546,7 +24546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>511</v>
       </c>
@@ -24587,7 +24587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>512</v>
       </c>
@@ -24631,7 +24631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>513</v>
       </c>
@@ -24672,7 +24672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>514</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>515</v>
       </c>
@@ -24754,7 +24754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>516</v>
       </c>
@@ -24795,7 +24795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>517</v>
       </c>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>518</v>
       </c>
@@ -24880,7 +24880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>519</v>
       </c>
@@ -24921,7 +24921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>520</v>
       </c>
@@ -24962,7 +24962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>521</v>
       </c>
@@ -25003,7 +25003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>522</v>
       </c>
@@ -25044,7 +25044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>523</v>
       </c>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>524</v>
       </c>
@@ -25126,7 +25126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>525</v>
       </c>
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>526</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>527</v>
       </c>
@@ -25249,7 +25249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>528</v>
       </c>
@@ -25290,7 +25290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>529</v>
       </c>
@@ -25331,7 +25331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>530</v>
       </c>
@@ -25372,7 +25372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>531</v>
       </c>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>532</v>
       </c>
@@ -25454,7 +25454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>533</v>
       </c>
@@ -25495,7 +25495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>534</v>
       </c>
@@ -25536,7 +25536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>535</v>
       </c>
@@ -25577,7 +25577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>536</v>
       </c>
@@ -25618,7 +25618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>537</v>
       </c>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>538</v>
       </c>
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>539</v>
       </c>
@@ -25744,7 +25744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>540</v>
       </c>
@@ -25785,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>541</v>
       </c>
@@ -25826,7 +25826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>542</v>
       </c>
@@ -25870,7 +25870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>543</v>
       </c>
@@ -25911,7 +25911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>544</v>
       </c>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>545</v>
       </c>
@@ -25996,7 +25996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>546</v>
       </c>
@@ -26040,7 +26040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>547</v>
       </c>
@@ -26081,7 +26081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>548</v>
       </c>
@@ -26125,7 +26125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>549</v>
       </c>
@@ -26166,7 +26166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>550</v>
       </c>
@@ -26207,7 +26207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>551</v>
       </c>
@@ -26248,7 +26248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>552</v>
       </c>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>553</v>
       </c>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>554</v>
       </c>
@@ -26371,7 +26371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>555</v>
       </c>
@@ -26415,7 +26415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>556</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>557</v>
       </c>
@@ -26497,7 +26497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>558</v>
       </c>
@@ -26538,7 +26538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>559</v>
       </c>
@@ -26579,7 +26579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>560</v>
       </c>
@@ -26623,7 +26623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>561</v>
       </c>
@@ -26667,7 +26667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>562</v>
       </c>
@@ -26708,7 +26708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>563</v>
       </c>
@@ -26749,7 +26749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>564</v>
       </c>
@@ -26790,7 +26790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>565</v>
       </c>
@@ -26831,7 +26831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>566</v>
       </c>
@@ -26872,7 +26872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>567</v>
       </c>
@@ -26913,7 +26913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>568</v>
       </c>
@@ -26954,7 +26954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>569</v>
       </c>
@@ -26995,7 +26995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>570</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>571</v>
       </c>
@@ -27077,7 +27077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>572</v>
       </c>
@@ -27118,7 +27118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>573</v>
       </c>
@@ -27162,7 +27162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>574</v>
       </c>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>575</v>
       </c>
@@ -27248,7 +27248,7 @@
         <v/>
       </c>
     </row>
-    <row r="565" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>576</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>577</v>
       </c>
@@ -27330,7 +27330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>578</v>
       </c>
@@ -27371,7 +27371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>579</v>
       </c>
@@ -27412,7 +27412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>580</v>
       </c>
@@ -27454,6 +27454,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N655">
+    <sortCondition ref="C1:C655"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B2:B655">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
